--- a/output/2026-09-14_03_Croazia_Licko-senjska_Cleaning.xlsx
+++ b/output/2026-09-14_03_Croazia_Licko-senjska_Cleaning.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Punto vendita di Gospić (IX GBR Hrvatske vojske 7) della stessa società Poljopromet d.o.o. Telefono confermato via ricerca (fonte azienda/poslovnice). Email specifica del punto vendita segue il pattern di dominio confermato (info@poljopromet.net) ma non è stata riscontrata verbatim in uno snippet indipendente: da verificare sul sito.</t>
+          <t>Punto vendita di Gospić (IX GBR Hrvatske vojske 7) della stessa società Poljopromet d.o.o. Telefono confermato via ricerca (fonte azienda/poslovnice). Email specifica del punto vendita segue il pattern di dominio confermato (info@poljopromet.net) ma non è stata riscontrata verbatim in uno snippet indipendente: da verificare sul sito. [DUPLICATO — vedi anche: 2026-09-14_03_Croazia_Licko-senjska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Punto vendita di Perušić (Zrinskih Frankopana 61) della stessa società Poljopromet d.o.o. Telefono confermato via ricerca. Email specifica del punto vendita segue il pattern di dominio confermato ma non riscontrata verbatim in uno snippet indipendente: da verificare sul sito.</t>
+          <t>Punto vendita di Perušić (Zrinskih Frankopana 61) della stessa società Poljopromet d.o.o. Telefono confermato via ricerca. Email specifica del punto vendita segue il pattern di dominio confermato ma non riscontrata verbatim in uno snippet indipendente: da verificare sul sito. [DUPLICATO — vedi anche: 2026-09-14_03_Croazia_Licko-senjska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -590,7 +590,6 @@
           <t>Martinčić d.o.o.</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Gospić - Ličko-senjska županija</t>
@@ -601,8 +600,6 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Azienda reale confermata (fininfo.hr, companywall.hr, elenco distributori Saint-Gobain Croazia). Attivita': ferramenta, materiali edili, vernici e vetro. Telefono non confermato con certezza: la lista originale riportava 053 573 446, ma le fonti pubbliche consultate (registri societari) riportano numeri diversi (053 560541 / 053 560520) senza un riscontro univoco; per prudenza il campo e' lasciato vuoto. Nessun sito ufficiale ne' email generica individuati. Gamma ferramenta/edilizia puo' includere articoli di pulizia di base, ma nessuna evidenza diretta di prodotti/attrezzature di pulizia industriale in assortimento.</t>
@@ -682,7 +679,6 @@
           <t>053 574 007</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Azienda reale confermata (fininfo.hr, companywall.hr, registri camerali; sito ufficiale vrkljan.hr con sezione 'Gradevinski materijal'). Attivita' mista: negozio di generi alimentari/non alimentari (supermercato) e materiali edili/vernici, 4 punti vendita (3 a Gospić, 1 a Lički Osik). Sito web non presente nella lista originale, individuato tramite ricerca. Telefono: fonti divergono tra 053 574 007 (Žute Stranice, Polomap) e 053 575 317/053 572 817 (lista originale, altre fonti), verosimilmente linee di punti vendita diversi dello stesso gruppo; riportato il numero piu' ricorrente nelle fonti indipendenti. Nessuna email generica individuata. Nessuna conferma diretta di prodotti/attrezzature di pulizia industriale in gamma; profilo coerente con rivenditore generalista misto (edilizia/generi vari) tipico dell'area rurale.</t>
@@ -700,7 +696,6 @@
           <t>Gramex-Comm d.o.o.</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Senj - Ličko-senjska županija</t>
@@ -716,7 +711,6 @@
           <t>053 882 555</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Azienda reale confermata (fininfo.hr, mojkvart.hr, poslovna.hr). Attivita' registrata: commercio all'ingrosso non specializzato, materiali edili e trasporto merci. Telefono confermato (corrisponde alla lista originale). Nessun sito ufficiale individuato. E' stata trovata solo un'email personale di un referente aziendale (non un indirizzo generico aziendale): per policy non viene riportata come email generica, campo lasciato vuoto. Nessuna evidenza diretta di prodotti/attrezzature di pulizia in gamma; profilo coerente con rivenditore edile generalista, in linea col contesto rurale della contea.</t>

--- a/output/2026-09-14_03_Croazia_Licko-senjska_Cleaning.xlsx
+++ b/output/2026-09-14_03_Croazia_Licko-senjska_Cleaning.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
